--- a/R.Choferes.xlsx
+++ b/R.Choferes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>REPORTE DE CHOFERES</t>
   </si>
@@ -62,31 +62,73 @@
     <t xml:space="preserve">Ganancia </t>
   </si>
   <si>
-    <t>Empresa</t>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Dias trabajados</t>
   </si>
   <si>
     <t>$400</t>
   </si>
   <si>
+    <t>$850</t>
+  </si>
+  <si>
+    <t>$450</t>
+  </si>
+  <si>
+    <t>$1000</t>
+  </si>
+  <si>
     <t>$800</t>
   </si>
   <si>
-    <t>TT</t>
+    <t>$600</t>
   </si>
   <si>
-    <t>2025-10-01 08:17:33</t>
+    <t>2025-10-03 09:46:50</t>
   </si>
   <si>
-    <t>g.otay</t>
+    <t xml:space="preserve">central </t>
   </si>
   <si>
     <t>Fernando</t>
   </si>
   <si>
-    <t>2025-10-01 08:17:41</t>
+    <t>2025-10-04 09:50:07</t>
   </si>
   <si>
-    <t xml:space="preserve">san isidro </t>
+    <t>centro</t>
+  </si>
+  <si>
+    <t>2025-10-03 10:08:34</t>
+  </si>
+  <si>
+    <t>g otay</t>
+  </si>
+  <si>
+    <t>pruebas</t>
+  </si>
+  <si>
+    <t>2025-10-03 10:10:51</t>
+  </si>
+  <si>
+    <t>clínica 27</t>
+  </si>
+  <si>
+    <t>victor</t>
+  </si>
+  <si>
+    <t>2025-10-03 10:21:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">easy park </t>
+  </si>
+  <si>
+    <t>2025-10-03 10:51:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recomendar hotel </t>
   </si>
 </sst>
 </file>
@@ -158,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -170,6 +212,9 @@
     <xf xfId="0" fontId="0" numFmtId="44" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -485,6 +530,7 @@
     <col min="12" max="12" width="15" customWidth="true" style="0"/>
     <col min="13" max="13" width="18.714285714286" customWidth="true" style="0"/>
     <col min="14" max="14" width="13.285714285714" customWidth="true" style="0"/>
+    <col min="15" max="15" width="20.571428571429" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -505,7 +551,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="5"/>
+      <c r="O1" s="1"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -524,7 +570,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="5"/>
+      <c r="O2" s="1"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
@@ -543,7 +589,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="5"/>
+      <c r="O3" s="1"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -562,7 +608,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="5"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
@@ -581,7 +627,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="5"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
@@ -602,7 +648,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="6"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
@@ -647,134 +693,249 @@
       <c r="N7" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="O7" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
-        <v>337302</v>
+        <v>337318</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8">
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8">
         <v>20</v>
       </c>
       <c r="M8" s="4">
         <f>IF(K8="","",K8/100*L8)</f>
-        <v>160</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="N8" s="7">
+        <v>2</v>
+      </c>
+      <c r="O8" s="8">
+        <v>2</v>
+      </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9">
-        <v>337303</v>
+        <v>337319</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="M9" s="4" t="str">
+        <v>19</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>10</v>
+      </c>
+      <c r="M9" s="4">
         <f>IF(K9="","",K9/100*L9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="N9" s="7">
+        <v>2</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1</v>
+      </c>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="G10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="M10" s="4" t="str">
+      <c r="A10">
+        <v>337320</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10">
+        <v>50</v>
+      </c>
+      <c r="M10" s="4">
         <f>IF(K10="","",K10/100*L10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="7"/>
-      <c r="O10" s="5"/>
+        <v>400</v>
+      </c>
+      <c r="N10" s="7">
+        <v>2</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1</v>
+      </c>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="G11" s="4"/>
+      <c r="A11">
+        <v>337321</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="M11" s="4" t="str">
         <f>IF(K11="","",K11/100*L11)</f>
         <v/>
       </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="5"/>
+      <c r="O11" s="8"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="G12" s="4"/>
+      <c r="A12">
+        <v>337322</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="M12" s="4" t="str">
         <f>IF(K12="","",K12/100*L12)</f>
         <v/>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="5"/>
+      <c r="O12" s="8"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="G13" s="4"/>
+      <c r="A13">
+        <v>337323</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="M13" s="4" t="str">
         <f>IF(K13="","",K13/100*L13)</f>
         <v/>
       </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="5"/>
+      <c r="O13" s="8"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
@@ -787,7 +948,7 @@
         <v/>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="6"/>
+      <c r="O14" s="8"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -800,6 +961,7 @@
         <v/>
       </c>
       <c r="N15" s="7"/>
+      <c r="O15" s="9"/>
     </row>
     <row r="16" spans="1:18">
       <c r="G16" s="4"/>
@@ -809,7 +971,7 @@
         <v/>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="5"/>
+      <c r="O16" s="8"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
@@ -822,7 +984,7 @@
         <v/>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="5"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
@@ -835,7 +997,7 @@
         <v/>
       </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="5"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
@@ -848,7 +1010,7 @@
         <v/>
       </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="5"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
@@ -861,7 +1023,7 @@
         <v/>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="5"/>
+      <c r="O20" s="8"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
@@ -874,7 +1036,7 @@
         <v/>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="5"/>
+      <c r="O21" s="8"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
@@ -887,7 +1049,7 @@
         <v/>
       </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="6"/>
+      <c r="O22" s="8"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -900,6 +1062,7 @@
         <v/>
       </c>
       <c r="N23" s="7"/>
+      <c r="O23" s="9"/>
     </row>
     <row r="24" spans="1:18">
       <c r="G24" s="4"/>
@@ -909,6 +1072,7 @@
         <v/>
       </c>
       <c r="N24" s="7"/>
+      <c r="O24" s="9"/>
     </row>
     <row r="25" spans="1:18">
       <c r="G25" s="4"/>
@@ -918,6 +1082,7 @@
         <v/>
       </c>
       <c r="N25" s="7"/>
+      <c r="O25" s="9"/>
     </row>
     <row r="26" spans="1:18">
       <c r="G26" s="4"/>
@@ -927,6 +1092,7 @@
         <v/>
       </c>
       <c r="N26" s="7"/>
+      <c r="O26" s="9"/>
     </row>
     <row r="27" spans="1:18">
       <c r="G27" s="4"/>
@@ -936,6 +1102,7 @@
         <v/>
       </c>
       <c r="N27" s="7"/>
+      <c r="O27" s="9"/>
     </row>
     <row r="28" spans="1:18">
       <c r="G28" s="4"/>
@@ -945,6 +1112,7 @@
         <v/>
       </c>
       <c r="N28" s="7"/>
+      <c r="O28" s="9"/>
     </row>
     <row r="29" spans="1:18">
       <c r="G29" s="4"/>
@@ -954,6 +1122,7 @@
         <v/>
       </c>
       <c r="N29" s="7"/>
+      <c r="O29" s="9"/>
     </row>
     <row r="30" spans="1:18">
       <c r="G30" s="4"/>
@@ -963,6 +1132,7 @@
         <v/>
       </c>
       <c r="N30" s="7"/>
+      <c r="O30" s="9"/>
     </row>
     <row r="31" spans="1:18">
       <c r="G31" s="4"/>
@@ -972,6 +1142,7 @@
         <v/>
       </c>
       <c r="N31" s="7"/>
+      <c r="O31" s="9"/>
     </row>
     <row r="32" spans="1:18">
       <c r="G32" s="4"/>
@@ -981,6 +1152,7 @@
         <v/>
       </c>
       <c r="N32" s="7"/>
+      <c r="O32" s="9"/>
     </row>
     <row r="33" spans="1:18">
       <c r="G33" s="4"/>
@@ -990,6 +1162,7 @@
         <v/>
       </c>
       <c r="N33" s="7"/>
+      <c r="O33" s="9"/>
     </row>
     <row r="34" spans="1:18">
       <c r="G34" s="4"/>
@@ -999,6 +1172,7 @@
         <v/>
       </c>
       <c r="N34" s="7"/>
+      <c r="O34" s="9"/>
     </row>
     <row r="35" spans="1:18">
       <c r="G35" s="4"/>
@@ -1008,6 +1182,7 @@
         <v/>
       </c>
       <c r="N35" s="7"/>
+      <c r="O35" s="9"/>
     </row>
     <row r="36" spans="1:18">
       <c r="G36" s="4"/>
@@ -1017,6 +1192,7 @@
         <v/>
       </c>
       <c r="N36" s="7"/>
+      <c r="O36" s="9"/>
     </row>
     <row r="37" spans="1:18">
       <c r="G37" s="4"/>
@@ -1026,6 +1202,7 @@
         <v/>
       </c>
       <c r="N37" s="7"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:18">
       <c r="G38" s="4"/>
@@ -1035,6 +1212,7 @@
         <v/>
       </c>
       <c r="N38" s="7"/>
+      <c r="O38" s="9"/>
     </row>
     <row r="39" spans="1:18">
       <c r="G39" s="4"/>
@@ -1044,6 +1222,7 @@
         <v/>
       </c>
       <c r="N39" s="7"/>
+      <c r="O39" s="9"/>
     </row>
     <row r="40" spans="1:18">
       <c r="G40" s="4"/>
@@ -1053,6 +1232,7 @@
         <v/>
       </c>
       <c r="N40" s="7"/>
+      <c r="O40" s="9"/>
     </row>
     <row r="41" spans="1:18">
       <c r="G41" s="4"/>
@@ -1062,6 +1242,7 @@
         <v/>
       </c>
       <c r="N41" s="7"/>
+      <c r="O41" s="9"/>
     </row>
     <row r="42" spans="1:18">
       <c r="G42" s="4"/>
@@ -1071,6 +1252,7 @@
         <v/>
       </c>
       <c r="N42" s="7"/>
+      <c r="O42" s="9"/>
     </row>
     <row r="43" spans="1:18">
       <c r="G43" s="4"/>
@@ -1080,6 +1262,7 @@
         <v/>
       </c>
       <c r="N43" s="7"/>
+      <c r="O43" s="9"/>
     </row>
     <row r="44" spans="1:18">
       <c r="G44" s="4"/>
@@ -1089,6 +1272,7 @@
         <v/>
       </c>
       <c r="N44" s="7"/>
+      <c r="O44" s="9"/>
     </row>
     <row r="45" spans="1:18">
       <c r="G45" s="4"/>
@@ -1098,6 +1282,7 @@
         <v/>
       </c>
       <c r="N45" s="7"/>
+      <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:18">
       <c r="G46" s="4"/>
@@ -1107,6 +1292,7 @@
         <v/>
       </c>
       <c r="N46" s="7"/>
+      <c r="O46" s="9"/>
     </row>
     <row r="47" spans="1:18">
       <c r="G47" s="4"/>
@@ -1116,6 +1302,7 @@
         <v/>
       </c>
       <c r="N47" s="7"/>
+      <c r="O47" s="9"/>
     </row>
     <row r="48" spans="1:18">
       <c r="G48" s="4"/>
@@ -1125,6 +1312,7 @@
         <v/>
       </c>
       <c r="N48" s="7"/>
+      <c r="O48" s="9"/>
     </row>
     <row r="49" spans="1:18">
       <c r="G49" s="4"/>
@@ -1134,6 +1322,7 @@
         <v/>
       </c>
       <c r="N49" s="7"/>
+      <c r="O49" s="9"/>
     </row>
     <row r="50" spans="1:18">
       <c r="G50" s="4"/>
@@ -1143,6 +1332,7 @@
         <v/>
       </c>
       <c r="N50" s="7"/>
+      <c r="O50" s="9"/>
     </row>
     <row r="51" spans="1:18">
       <c r="G51" s="4"/>
@@ -1152,6 +1342,7 @@
         <v/>
       </c>
       <c r="N51" s="7"/>
+      <c r="O51" s="9"/>
     </row>
     <row r="52" spans="1:18">
       <c r="G52" s="4"/>
@@ -1161,6 +1352,7 @@
         <v/>
       </c>
       <c r="N52" s="7"/>
+      <c r="O52" s="9"/>
     </row>
     <row r="53" spans="1:18">
       <c r="G53" s="4"/>
@@ -1170,6 +1362,7 @@
         <v/>
       </c>
       <c r="N53" s="7"/>
+      <c r="O53" s="9"/>
     </row>
     <row r="54" spans="1:18">
       <c r="G54" s="4"/>
@@ -1179,6 +1372,7 @@
         <v/>
       </c>
       <c r="N54" s="7"/>
+      <c r="O54" s="9"/>
     </row>
     <row r="55" spans="1:18">
       <c r="G55" s="4"/>
@@ -1188,6 +1382,7 @@
         <v/>
       </c>
       <c r="N55" s="7"/>
+      <c r="O55" s="9"/>
     </row>
     <row r="56" spans="1:18">
       <c r="G56" s="4"/>
@@ -1197,6 +1392,7 @@
         <v/>
       </c>
       <c r="N56" s="7"/>
+      <c r="O56" s="9"/>
     </row>
     <row r="57" spans="1:18">
       <c r="G57" s="4"/>
@@ -1206,6 +1402,7 @@
         <v/>
       </c>
       <c r="N57" s="7"/>
+      <c r="O57" s="9"/>
     </row>
     <row r="58" spans="1:18">
       <c r="G58" s="4"/>
@@ -1215,6 +1412,7 @@
         <v/>
       </c>
       <c r="N58" s="7"/>
+      <c r="O58" s="9"/>
     </row>
     <row r="59" spans="1:18">
       <c r="G59" s="4"/>
@@ -1224,6 +1422,7 @@
         <v/>
       </c>
       <c r="N59" s="7"/>
+      <c r="O59" s="9"/>
     </row>
     <row r="60" spans="1:18">
       <c r="G60" s="4"/>
@@ -1233,6 +1432,7 @@
         <v/>
       </c>
       <c r="N60" s="7"/>
+      <c r="O60" s="9"/>
     </row>
     <row r="61" spans="1:18">
       <c r="G61" s="4"/>
@@ -1242,6 +1442,7 @@
         <v/>
       </c>
       <c r="N61" s="7"/>
+      <c r="O61" s="9"/>
     </row>
     <row r="62" spans="1:18">
       <c r="G62" s="4"/>
@@ -1251,6 +1452,7 @@
         <v/>
       </c>
       <c r="N62" s="7"/>
+      <c r="O62" s="9"/>
     </row>
     <row r="63" spans="1:18">
       <c r="G63" s="4"/>
@@ -1260,6 +1462,7 @@
         <v/>
       </c>
       <c r="N63" s="7"/>
+      <c r="O63" s="9"/>
     </row>
     <row r="64" spans="1:18">
       <c r="G64" s="4"/>
@@ -1269,6 +1472,7 @@
         <v/>
       </c>
       <c r="N64" s="7"/>
+      <c r="O64" s="9"/>
     </row>
     <row r="65" spans="1:18">
       <c r="G65" s="4"/>
@@ -1278,6 +1482,7 @@
         <v/>
       </c>
       <c r="N65" s="7"/>
+      <c r="O65" s="9"/>
     </row>
     <row r="66" spans="1:18">
       <c r="G66" s="4"/>
@@ -1287,6 +1492,7 @@
         <v/>
       </c>
       <c r="N66" s="7"/>
+      <c r="O66" s="9"/>
     </row>
     <row r="67" spans="1:18">
       <c r="G67" s="4"/>
@@ -1296,6 +1502,7 @@
         <v/>
       </c>
       <c r="N67" s="7"/>
+      <c r="O67" s="9"/>
     </row>
     <row r="68" spans="1:18">
       <c r="G68" s="4"/>
@@ -1305,6 +1512,7 @@
         <v/>
       </c>
       <c r="N68" s="7"/>
+      <c r="O68" s="9"/>
     </row>
     <row r="69" spans="1:18">
       <c r="G69" s="4"/>
@@ -1314,6 +1522,7 @@
         <v/>
       </c>
       <c r="N69" s="7"/>
+      <c r="O69" s="9"/>
     </row>
     <row r="70" spans="1:18">
       <c r="G70" s="4"/>
@@ -1323,6 +1532,7 @@
         <v/>
       </c>
       <c r="N70" s="7"/>
+      <c r="O70" s="9"/>
     </row>
     <row r="71" spans="1:18">
       <c r="G71" s="4"/>
@@ -1332,6 +1542,7 @@
         <v/>
       </c>
       <c r="N71" s="7"/>
+      <c r="O71" s="9"/>
     </row>
     <row r="72" spans="1:18">
       <c r="G72" s="4"/>
@@ -1341,6 +1552,7 @@
         <v/>
       </c>
       <c r="N72" s="7"/>
+      <c r="O72" s="9"/>
     </row>
     <row r="73" spans="1:18">
       <c r="G73" s="4"/>
@@ -1350,6 +1562,7 @@
         <v/>
       </c>
       <c r="N73" s="7"/>
+      <c r="O73" s="9"/>
     </row>
     <row r="74" spans="1:18">
       <c r="G74" s="4"/>
@@ -1359,6 +1572,7 @@
         <v/>
       </c>
       <c r="N74" s="7"/>
+      <c r="O74" s="9"/>
     </row>
     <row r="75" spans="1:18">
       <c r="G75" s="4"/>
@@ -1368,6 +1582,7 @@
         <v/>
       </c>
       <c r="N75" s="7"/>
+      <c r="O75" s="9"/>
     </row>
     <row r="76" spans="1:18">
       <c r="G76" s="4"/>
@@ -1377,6 +1592,7 @@
         <v/>
       </c>
       <c r="N76" s="7"/>
+      <c r="O76" s="9"/>
     </row>
     <row r="77" spans="1:18">
       <c r="G77" s="4"/>
@@ -1386,6 +1602,7 @@
         <v/>
       </c>
       <c r="N77" s="7"/>
+      <c r="O77" s="9"/>
     </row>
     <row r="78" spans="1:18">
       <c r="G78" s="4"/>
@@ -1395,6 +1612,7 @@
         <v/>
       </c>
       <c r="N78" s="7"/>
+      <c r="O78" s="9"/>
     </row>
     <row r="79" spans="1:18">
       <c r="G79" s="4"/>
@@ -1404,6 +1622,7 @@
         <v/>
       </c>
       <c r="N79" s="7"/>
+      <c r="O79" s="9"/>
     </row>
     <row r="80" spans="1:18">
       <c r="G80" s="4"/>
@@ -1413,6 +1632,7 @@
         <v/>
       </c>
       <c r="N80" s="7"/>
+      <c r="O80" s="9"/>
     </row>
     <row r="81" spans="1:18">
       <c r="G81" s="4"/>
@@ -1422,6 +1642,7 @@
         <v/>
       </c>
       <c r="N81" s="7"/>
+      <c r="O81" s="9"/>
     </row>
     <row r="82" spans="1:18">
       <c r="G82" s="4"/>
@@ -1431,6 +1652,7 @@
         <v/>
       </c>
       <c r="N82" s="7"/>
+      <c r="O82" s="9"/>
     </row>
     <row r="83" spans="1:18">
       <c r="G83" s="4"/>
@@ -1440,6 +1662,7 @@
         <v/>
       </c>
       <c r="N83" s="7"/>
+      <c r="O83" s="9"/>
     </row>
     <row r="84" spans="1:18">
       <c r="G84" s="4"/>
@@ -1449,6 +1672,7 @@
         <v/>
       </c>
       <c r="N84" s="7"/>
+      <c r="O84" s="9"/>
     </row>
     <row r="85" spans="1:18">
       <c r="G85" s="4"/>
@@ -1458,6 +1682,7 @@
         <v/>
       </c>
       <c r="N85" s="7"/>
+      <c r="O85" s="9"/>
     </row>
     <row r="86" spans="1:18">
       <c r="G86" s="4"/>
@@ -1467,6 +1692,7 @@
         <v/>
       </c>
       <c r="N86" s="7"/>
+      <c r="O86" s="9"/>
     </row>
     <row r="87" spans="1:18">
       <c r="G87" s="4"/>
@@ -1476,6 +1702,7 @@
         <v/>
       </c>
       <c r="N87" s="7"/>
+      <c r="O87" s="9"/>
     </row>
     <row r="88" spans="1:18">
       <c r="G88" s="4"/>
@@ -1485,6 +1712,7 @@
         <v/>
       </c>
       <c r="N88" s="7"/>
+      <c r="O88" s="9"/>
     </row>
     <row r="89" spans="1:18">
       <c r="G89" s="4"/>
@@ -1494,6 +1722,7 @@
         <v/>
       </c>
       <c r="N89" s="7"/>
+      <c r="O89" s="9"/>
     </row>
     <row r="90" spans="1:18">
       <c r="G90" s="4"/>
@@ -1503,6 +1732,7 @@
         <v/>
       </c>
       <c r="N90" s="7"/>
+      <c r="O90" s="9"/>
     </row>
     <row r="91" spans="1:18">
       <c r="G91" s="4"/>
@@ -1512,6 +1742,7 @@
         <v/>
       </c>
       <c r="N91" s="7"/>
+      <c r="O91" s="9"/>
     </row>
     <row r="92" spans="1:18">
       <c r="G92" s="4"/>
@@ -1521,6 +1752,7 @@
         <v/>
       </c>
       <c r="N92" s="7"/>
+      <c r="O92" s="9"/>
     </row>
     <row r="93" spans="1:18">
       <c r="G93" s="4"/>
@@ -1530,6 +1762,7 @@
         <v/>
       </c>
       <c r="N93" s="7"/>
+      <c r="O93" s="9"/>
     </row>
     <row r="94" spans="1:18">
       <c r="G94" s="4"/>
@@ -1539,6 +1772,7 @@
         <v/>
       </c>
       <c r="N94" s="7"/>
+      <c r="O94" s="9"/>
     </row>
     <row r="95" spans="1:18">
       <c r="G95" s="4"/>
@@ -1548,6 +1782,7 @@
         <v/>
       </c>
       <c r="N95" s="7"/>
+      <c r="O95" s="9"/>
     </row>
     <row r="96" spans="1:18">
       <c r="G96" s="4"/>
@@ -1557,6 +1792,7 @@
         <v/>
       </c>
       <c r="N96" s="7"/>
+      <c r="O96" s="9"/>
     </row>
     <row r="97" spans="1:18">
       <c r="G97" s="4"/>
@@ -1566,6 +1802,7 @@
         <v/>
       </c>
       <c r="N97" s="7"/>
+      <c r="O97" s="9"/>
     </row>
     <row r="98" spans="1:18">
       <c r="G98" s="4"/>
@@ -1575,6 +1812,7 @@
         <v/>
       </c>
       <c r="N98" s="7"/>
+      <c r="O98" s="9"/>
     </row>
     <row r="99" spans="1:18">
       <c r="G99" s="4"/>
@@ -1584,6 +1822,7 @@
         <v/>
       </c>
       <c r="N99" s="7"/>
+      <c r="O99" s="9"/>
     </row>
     <row r="100" spans="1:18">
       <c r="G100" s="4"/>
@@ -1593,6 +1832,7 @@
         <v/>
       </c>
       <c r="N100" s="7"/>
+      <c r="O100" s="9"/>
     </row>
     <row r="101" spans="1:18">
       <c r="G101" s="4"/>
@@ -1602,6 +1842,7 @@
         <v/>
       </c>
       <c r="N101" s="7"/>
+      <c r="O101" s="9"/>
     </row>
     <row r="102" spans="1:18">
       <c r="G102" s="4"/>
@@ -1611,6 +1852,7 @@
         <v/>
       </c>
       <c r="N102" s="7"/>
+      <c r="O102" s="9"/>
     </row>
     <row r="103" spans="1:18">
       <c r="G103" s="4"/>
@@ -1620,6 +1862,7 @@
         <v/>
       </c>
       <c r="N103" s="7"/>
+      <c r="O103" s="9"/>
     </row>
     <row r="104" spans="1:18">
       <c r="G104" s="4"/>
@@ -1629,6 +1872,7 @@
         <v/>
       </c>
       <c r="N104" s="7"/>
+      <c r="O104" s="9"/>
     </row>
     <row r="105" spans="1:18">
       <c r="G105" s="4"/>
@@ -1638,6 +1882,7 @@
         <v/>
       </c>
       <c r="N105" s="7"/>
+      <c r="O105" s="9"/>
     </row>
     <row r="106" spans="1:18">
       <c r="G106" s="4"/>
@@ -1647,6 +1892,7 @@
         <v/>
       </c>
       <c r="N106" s="7"/>
+      <c r="O106" s="9"/>
     </row>
     <row r="107" spans="1:18">
       <c r="G107" s="4"/>
@@ -1656,6 +1902,7 @@
         <v/>
       </c>
       <c r="N107" s="7"/>
+      <c r="O107" s="9"/>
     </row>
     <row r="108" spans="1:18">
       <c r="G108" s="4"/>
@@ -1665,6 +1912,7 @@
         <v/>
       </c>
       <c r="N108" s="7"/>
+      <c r="O108" s="9"/>
     </row>
     <row r="109" spans="1:18">
       <c r="G109" s="4"/>
@@ -1674,6 +1922,7 @@
         <v/>
       </c>
       <c r="N109" s="7"/>
+      <c r="O109" s="9"/>
     </row>
     <row r="110" spans="1:18">
       <c r="G110" s="4"/>
@@ -1683,6 +1932,7 @@
         <v/>
       </c>
       <c r="N110" s="7"/>
+      <c r="O110" s="9"/>
     </row>
     <row r="111" spans="1:18">
       <c r="G111" s="4"/>
@@ -1692,6 +1942,7 @@
         <v/>
       </c>
       <c r="N111" s="7"/>
+      <c r="O111" s="9"/>
     </row>
     <row r="112" spans="1:18">
       <c r="G112" s="4"/>
@@ -1701,6 +1952,7 @@
         <v/>
       </c>
       <c r="N112" s="7"/>
+      <c r="O112" s="9"/>
     </row>
     <row r="113" spans="1:18">
       <c r="G113" s="4"/>
@@ -1710,6 +1962,7 @@
         <v/>
       </c>
       <c r="N113" s="7"/>
+      <c r="O113" s="9"/>
     </row>
     <row r="114" spans="1:18">
       <c r="G114" s="4"/>
@@ -1719,6 +1972,7 @@
         <v/>
       </c>
       <c r="N114" s="7"/>
+      <c r="O114" s="9"/>
     </row>
     <row r="115" spans="1:18">
       <c r="G115" s="4"/>
@@ -1728,6 +1982,7 @@
         <v/>
       </c>
       <c r="N115" s="7"/>
+      <c r="O115" s="9"/>
     </row>
     <row r="116" spans="1:18">
       <c r="G116" s="4"/>
@@ -1737,6 +1992,7 @@
         <v/>
       </c>
       <c r="N116" s="7"/>
+      <c r="O116" s="9"/>
     </row>
     <row r="117" spans="1:18">
       <c r="G117" s="4"/>
@@ -1746,6 +2002,7 @@
         <v/>
       </c>
       <c r="N117" s="7"/>
+      <c r="O117" s="9"/>
     </row>
     <row r="118" spans="1:18">
       <c r="G118" s="4"/>
@@ -1755,6 +2012,7 @@
         <v/>
       </c>
       <c r="N118" s="7"/>
+      <c r="O118" s="9"/>
     </row>
     <row r="119" spans="1:18">
       <c r="G119" s="4"/>
@@ -1764,6 +2022,7 @@
         <v/>
       </c>
       <c r="N119" s="7"/>
+      <c r="O119" s="9"/>
     </row>
     <row r="120" spans="1:18">
       <c r="G120" s="4"/>
@@ -1773,6 +2032,7 @@
         <v/>
       </c>
       <c r="N120" s="7"/>
+      <c r="O120" s="9"/>
     </row>
     <row r="121" spans="1:18">
       <c r="G121" s="4"/>
@@ -1782,6 +2042,7 @@
         <v/>
       </c>
       <c r="N121" s="7"/>
+      <c r="O121" s="9"/>
     </row>
     <row r="122" spans="1:18">
       <c r="G122" s="4"/>
@@ -1791,6 +2052,7 @@
         <v/>
       </c>
       <c r="N122" s="7"/>
+      <c r="O122" s="9"/>
     </row>
     <row r="123" spans="1:18">
       <c r="G123" s="4"/>
@@ -1800,6 +2062,7 @@
         <v/>
       </c>
       <c r="N123" s="7"/>
+      <c r="O123" s="9"/>
     </row>
     <row r="124" spans="1:18">
       <c r="G124" s="4"/>
@@ -1809,6 +2072,7 @@
         <v/>
       </c>
       <c r="N124" s="7"/>
+      <c r="O124" s="9"/>
     </row>
     <row r="125" spans="1:18">
       <c r="G125" s="4"/>
@@ -1818,6 +2082,7 @@
         <v/>
       </c>
       <c r="N125" s="7"/>
+      <c r="O125" s="9"/>
     </row>
     <row r="126" spans="1:18">
       <c r="G126" s="4"/>
@@ -1827,6 +2092,7 @@
         <v/>
       </c>
       <c r="N126" s="7"/>
+      <c r="O126" s="9"/>
     </row>
     <row r="127" spans="1:18">
       <c r="G127" s="4"/>
@@ -1836,6 +2102,7 @@
         <v/>
       </c>
       <c r="N127" s="7"/>
+      <c r="O127" s="9"/>
     </row>
     <row r="128" spans="1:18">
       <c r="G128" s="4"/>
@@ -1845,6 +2112,7 @@
         <v/>
       </c>
       <c r="N128" s="7"/>
+      <c r="O128" s="9"/>
     </row>
     <row r="129" spans="1:18">
       <c r="G129" s="4"/>
@@ -1854,6 +2122,7 @@
         <v/>
       </c>
       <c r="N129" s="7"/>
+      <c r="O129" s="9"/>
     </row>
     <row r="130" spans="1:18">
       <c r="G130" s="4"/>
@@ -1863,6 +2132,7 @@
         <v/>
       </c>
       <c r="N130" s="7"/>
+      <c r="O130" s="9"/>
     </row>
     <row r="131" spans="1:18">
       <c r="G131" s="4"/>
@@ -1872,6 +2142,7 @@
         <v/>
       </c>
       <c r="N131" s="7"/>
+      <c r="O131" s="9"/>
     </row>
     <row r="132" spans="1:18">
       <c r="G132" s="4"/>
@@ -1881,6 +2152,7 @@
         <v/>
       </c>
       <c r="N132" s="7"/>
+      <c r="O132" s="9"/>
     </row>
     <row r="133" spans="1:18">
       <c r="G133" s="4"/>
@@ -1890,6 +2162,7 @@
         <v/>
       </c>
       <c r="N133" s="7"/>
+      <c r="O133" s="9"/>
     </row>
     <row r="134" spans="1:18">
       <c r="G134" s="4"/>
@@ -1899,6 +2172,7 @@
         <v/>
       </c>
       <c r="N134" s="7"/>
+      <c r="O134" s="9"/>
     </row>
     <row r="135" spans="1:18">
       <c r="G135" s="4"/>
@@ -1908,6 +2182,7 @@
         <v/>
       </c>
       <c r="N135" s="7"/>
+      <c r="O135" s="9"/>
     </row>
     <row r="136" spans="1:18">
       <c r="G136" s="4"/>
@@ -1917,6 +2192,7 @@
         <v/>
       </c>
       <c r="N136" s="7"/>
+      <c r="O136" s="9"/>
     </row>
     <row r="137" spans="1:18">
       <c r="G137" s="4"/>
@@ -1926,6 +2202,7 @@
         <v/>
       </c>
       <c r="N137" s="7"/>
+      <c r="O137" s="9"/>
     </row>
     <row r="138" spans="1:18">
       <c r="G138" s="4"/>
@@ -1935,6 +2212,7 @@
         <v/>
       </c>
       <c r="N138" s="7"/>
+      <c r="O138" s="9"/>
     </row>
     <row r="139" spans="1:18">
       <c r="G139" s="4"/>
@@ -1944,6 +2222,7 @@
         <v/>
       </c>
       <c r="N139" s="7"/>
+      <c r="O139" s="9"/>
     </row>
     <row r="140" spans="1:18">
       <c r="G140" s="4"/>
@@ -1953,6 +2232,7 @@
         <v/>
       </c>
       <c r="N140" s="7"/>
+      <c r="O140" s="9"/>
     </row>
     <row r="141" spans="1:18">
       <c r="G141" s="4"/>
@@ -1962,6 +2242,7 @@
         <v/>
       </c>
       <c r="N141" s="7"/>
+      <c r="O141" s="9"/>
     </row>
     <row r="142" spans="1:18">
       <c r="G142" s="4"/>
@@ -1971,6 +2252,7 @@
         <v/>
       </c>
       <c r="N142" s="7"/>
+      <c r="O142" s="9"/>
     </row>
     <row r="143" spans="1:18">
       <c r="G143" s="4"/>
@@ -1980,6 +2262,7 @@
         <v/>
       </c>
       <c r="N143" s="7"/>
+      <c r="O143" s="9"/>
     </row>
     <row r="144" spans="1:18">
       <c r="G144" s="4"/>
@@ -1989,6 +2272,7 @@
         <v/>
       </c>
       <c r="N144" s="7"/>
+      <c r="O144" s="9"/>
     </row>
     <row r="145" spans="1:18">
       <c r="G145" s="4"/>
@@ -1998,6 +2282,7 @@
         <v/>
       </c>
       <c r="N145" s="7"/>
+      <c r="O145" s="9"/>
     </row>
     <row r="146" spans="1:18">
       <c r="G146" s="4"/>
@@ -2007,6 +2292,7 @@
         <v/>
       </c>
       <c r="N146" s="7"/>
+      <c r="O146" s="9"/>
     </row>
     <row r="147" spans="1:18">
       <c r="G147" s="4"/>
@@ -2016,6 +2302,7 @@
         <v/>
       </c>
       <c r="N147" s="7"/>
+      <c r="O147" s="9"/>
     </row>
     <row r="148" spans="1:18">
       <c r="G148" s="4"/>
@@ -2025,6 +2312,7 @@
         <v/>
       </c>
       <c r="N148" s="7"/>
+      <c r="O148" s="9"/>
     </row>
     <row r="149" spans="1:18">
       <c r="G149" s="4"/>
@@ -2034,6 +2322,7 @@
         <v/>
       </c>
       <c r="N149" s="7"/>
+      <c r="O149" s="9"/>
     </row>
     <row r="150" spans="1:18">
       <c r="G150" s="4"/>
@@ -2043,6 +2332,7 @@
         <v/>
       </c>
       <c r="N150" s="7"/>
+      <c r="O150" s="9"/>
     </row>
     <row r="151" spans="1:18">
       <c r="G151" s="4"/>
@@ -2052,6 +2342,7 @@
         <v/>
       </c>
       <c r="N151" s="7"/>
+      <c r="O151" s="9"/>
     </row>
     <row r="152" spans="1:18">
       <c r="G152" s="4"/>
@@ -2061,6 +2352,7 @@
         <v/>
       </c>
       <c r="N152" s="7"/>
+      <c r="O152" s="9"/>
     </row>
     <row r="153" spans="1:18">
       <c r="G153" s="4"/>
@@ -2070,6 +2362,7 @@
         <v/>
       </c>
       <c r="N153" s="7"/>
+      <c r="O153" s="9"/>
     </row>
     <row r="154" spans="1:18">
       <c r="G154" s="4"/>
@@ -2079,6 +2372,7 @@
         <v/>
       </c>
       <c r="N154" s="7"/>
+      <c r="O154" s="9"/>
     </row>
     <row r="155" spans="1:18">
       <c r="G155" s="4"/>
@@ -2088,6 +2382,7 @@
         <v/>
       </c>
       <c r="N155" s="7"/>
+      <c r="O155" s="9"/>
     </row>
     <row r="156" spans="1:18">
       <c r="G156" s="4"/>
@@ -2097,6 +2392,7 @@
         <v/>
       </c>
       <c r="N156" s="7"/>
+      <c r="O156" s="9"/>
     </row>
     <row r="157" spans="1:18">
       <c r="G157" s="4"/>
@@ -2106,6 +2402,7 @@
         <v/>
       </c>
       <c r="N157" s="7"/>
+      <c r="O157" s="9"/>
     </row>
     <row r="158" spans="1:18">
       <c r="G158" s="4"/>
@@ -2115,6 +2412,7 @@
         <v/>
       </c>
       <c r="N158" s="7"/>
+      <c r="O158" s="9"/>
     </row>
     <row r="159" spans="1:18">
       <c r="G159" s="4"/>
@@ -2124,6 +2422,7 @@
         <v/>
       </c>
       <c r="N159" s="7"/>
+      <c r="O159" s="9"/>
     </row>
     <row r="160" spans="1:18">
       <c r="G160" s="4"/>
@@ -2133,6 +2432,7 @@
         <v/>
       </c>
       <c r="N160" s="7"/>
+      <c r="O160" s="9"/>
     </row>
     <row r="161" spans="1:18">
       <c r="G161" s="4"/>
@@ -2142,6 +2442,7 @@
         <v/>
       </c>
       <c r="N161" s="7"/>
+      <c r="O161" s="9"/>
     </row>
     <row r="162" spans="1:18">
       <c r="G162" s="4"/>
@@ -2151,6 +2452,7 @@
         <v/>
       </c>
       <c r="N162" s="7"/>
+      <c r="O162" s="9"/>
     </row>
     <row r="163" spans="1:18">
       <c r="G163" s="4"/>
@@ -2160,6 +2462,7 @@
         <v/>
       </c>
       <c r="N163" s="7"/>
+      <c r="O163" s="9"/>
     </row>
     <row r="164" spans="1:18">
       <c r="G164" s="4"/>
@@ -2169,6 +2472,7 @@
         <v/>
       </c>
       <c r="N164" s="7"/>
+      <c r="O164" s="9"/>
     </row>
     <row r="165" spans="1:18">
       <c r="G165" s="4"/>
@@ -2178,6 +2482,7 @@
         <v/>
       </c>
       <c r="N165" s="7"/>
+      <c r="O165" s="9"/>
     </row>
     <row r="166" spans="1:18">
       <c r="G166" s="4"/>
@@ -2187,6 +2492,7 @@
         <v/>
       </c>
       <c r="N166" s="7"/>
+      <c r="O166" s="9"/>
     </row>
     <row r="167" spans="1:18">
       <c r="G167" s="4"/>
@@ -2196,6 +2502,7 @@
         <v/>
       </c>
       <c r="N167" s="7"/>
+      <c r="O167" s="9"/>
     </row>
     <row r="168" spans="1:18">
       <c r="G168" s="4"/>
@@ -2205,6 +2512,7 @@
         <v/>
       </c>
       <c r="N168" s="7"/>
+      <c r="O168" s="9"/>
     </row>
     <row r="169" spans="1:18">
       <c r="G169" s="4"/>
@@ -2214,6 +2522,7 @@
         <v/>
       </c>
       <c r="N169" s="7"/>
+      <c r="O169" s="9"/>
     </row>
     <row r="170" spans="1:18">
       <c r="G170" s="4"/>
@@ -2223,6 +2532,7 @@
         <v/>
       </c>
       <c r="N170" s="7"/>
+      <c r="O170" s="9"/>
     </row>
     <row r="171" spans="1:18">
       <c r="G171" s="4"/>
@@ -2232,6 +2542,7 @@
         <v/>
       </c>
       <c r="N171" s="7"/>
+      <c r="O171" s="9"/>
     </row>
     <row r="172" spans="1:18">
       <c r="G172" s="4"/>
@@ -2241,6 +2552,7 @@
         <v/>
       </c>
       <c r="N172" s="7"/>
+      <c r="O172" s="9"/>
     </row>
     <row r="173" spans="1:18">
       <c r="G173" s="4"/>
@@ -2250,6 +2562,7 @@
         <v/>
       </c>
       <c r="N173" s="7"/>
+      <c r="O173" s="9"/>
     </row>
     <row r="174" spans="1:18">
       <c r="G174" s="4"/>
@@ -2259,6 +2572,7 @@
         <v/>
       </c>
       <c r="N174" s="7"/>
+      <c r="O174" s="9"/>
     </row>
     <row r="175" spans="1:18">
       <c r="G175" s="4"/>
@@ -2268,6 +2582,7 @@
         <v/>
       </c>
       <c r="N175" s="7"/>
+      <c r="O175" s="9"/>
     </row>
     <row r="176" spans="1:18">
       <c r="G176" s="4"/>
@@ -2277,6 +2592,7 @@
         <v/>
       </c>
       <c r="N176" s="7"/>
+      <c r="O176" s="9"/>
     </row>
     <row r="177" spans="1:18">
       <c r="G177" s="4"/>
@@ -2286,6 +2602,7 @@
         <v/>
       </c>
       <c r="N177" s="7"/>
+      <c r="O177" s="9"/>
     </row>
     <row r="178" spans="1:18">
       <c r="G178" s="4"/>
@@ -2295,6 +2612,7 @@
         <v/>
       </c>
       <c r="N178" s="7"/>
+      <c r="O178" s="9"/>
     </row>
     <row r="179" spans="1:18">
       <c r="G179" s="4"/>
@@ -2304,6 +2622,7 @@
         <v/>
       </c>
       <c r="N179" s="7"/>
+      <c r="O179" s="9"/>
     </row>
     <row r="180" spans="1:18">
       <c r="G180" s="4"/>
@@ -2313,6 +2632,7 @@
         <v/>
       </c>
       <c r="N180" s="7"/>
+      <c r="O180" s="9"/>
     </row>
     <row r="181" spans="1:18">
       <c r="G181" s="4"/>
@@ -2322,6 +2642,7 @@
         <v/>
       </c>
       <c r="N181" s="7"/>
+      <c r="O181" s="9"/>
     </row>
     <row r="182" spans="1:18">
       <c r="G182" s="4"/>
@@ -2331,6 +2652,7 @@
         <v/>
       </c>
       <c r="N182" s="7"/>
+      <c r="O182" s="9"/>
     </row>
     <row r="183" spans="1:18">
       <c r="G183" s="4"/>
@@ -2340,6 +2662,7 @@
         <v/>
       </c>
       <c r="N183" s="7"/>
+      <c r="O183" s="9"/>
     </row>
     <row r="184" spans="1:18">
       <c r="G184" s="4"/>
@@ -2349,6 +2672,7 @@
         <v/>
       </c>
       <c r="N184" s="7"/>
+      <c r="O184" s="9"/>
     </row>
     <row r="185" spans="1:18">
       <c r="G185" s="4"/>
@@ -2358,6 +2682,7 @@
         <v/>
       </c>
       <c r="N185" s="7"/>
+      <c r="O185" s="9"/>
     </row>
     <row r="186" spans="1:18">
       <c r="G186" s="4"/>
@@ -2367,6 +2692,7 @@
         <v/>
       </c>
       <c r="N186" s="7"/>
+      <c r="O186" s="9"/>
     </row>
     <row r="187" spans="1:18">
       <c r="G187" s="4"/>
@@ -2376,6 +2702,7 @@
         <v/>
       </c>
       <c r="N187" s="7"/>
+      <c r="O187" s="9"/>
     </row>
     <row r="188" spans="1:18">
       <c r="G188" s="4"/>
@@ -2385,6 +2712,7 @@
         <v/>
       </c>
       <c r="N188" s="7"/>
+      <c r="O188" s="9"/>
     </row>
     <row r="189" spans="1:18">
       <c r="G189" s="4"/>
@@ -2394,6 +2722,7 @@
         <v/>
       </c>
       <c r="N189" s="7"/>
+      <c r="O189" s="9"/>
     </row>
     <row r="190" spans="1:18">
       <c r="G190" s="4"/>
@@ -2403,6 +2732,7 @@
         <v/>
       </c>
       <c r="N190" s="7"/>
+      <c r="O190" s="9"/>
     </row>
     <row r="191" spans="1:18">
       <c r="G191" s="4"/>
@@ -2412,6 +2742,7 @@
         <v/>
       </c>
       <c r="N191" s="7"/>
+      <c r="O191" s="9"/>
     </row>
     <row r="192" spans="1:18">
       <c r="G192" s="4"/>
@@ -2421,6 +2752,7 @@
         <v/>
       </c>
       <c r="N192" s="7"/>
+      <c r="O192" s="9"/>
     </row>
     <row r="193" spans="1:18">
       <c r="G193" s="4"/>
@@ -2430,6 +2762,7 @@
         <v/>
       </c>
       <c r="N193" s="7"/>
+      <c r="O193" s="9"/>
     </row>
     <row r="194" spans="1:18">
       <c r="G194" s="4"/>
@@ -2439,6 +2772,7 @@
         <v/>
       </c>
       <c r="N194" s="7"/>
+      <c r="O194" s="9"/>
     </row>
     <row r="195" spans="1:18">
       <c r="G195" s="4"/>
@@ -2448,6 +2782,7 @@
         <v/>
       </c>
       <c r="N195" s="7"/>
+      <c r="O195" s="9"/>
     </row>
     <row r="196" spans="1:18">
       <c r="G196" s="4"/>
@@ -2457,6 +2792,7 @@
         <v/>
       </c>
       <c r="N196" s="7"/>
+      <c r="O196" s="9"/>
     </row>
     <row r="197" spans="1:18">
       <c r="G197" s="4"/>
@@ -2466,6 +2802,7 @@
         <v/>
       </c>
       <c r="N197" s="7"/>
+      <c r="O197" s="9"/>
     </row>
     <row r="198" spans="1:18">
       <c r="G198" s="4"/>
@@ -2475,6 +2812,7 @@
         <v/>
       </c>
       <c r="N198" s="7"/>
+      <c r="O198" s="9"/>
     </row>
     <row r="199" spans="1:18">
       <c r="G199" s="4"/>
@@ -2484,6 +2822,7 @@
         <v/>
       </c>
       <c r="N199" s="7"/>
+      <c r="O199" s="9"/>
     </row>
     <row r="200" spans="1:18">
       <c r="G200" s="4"/>
@@ -2493,6 +2832,7 @@
         <v/>
       </c>
       <c r="N200" s="7"/>
+      <c r="O200" s="9"/>
     </row>
     <row r="201" spans="1:18">
       <c r="G201" s="4"/>
@@ -2502,6 +2842,7 @@
         <v/>
       </c>
       <c r="N201" s="7"/>
+      <c r="O201" s="9"/>
     </row>
     <row r="202" spans="1:18">
       <c r="G202" s="4"/>
@@ -2511,6 +2852,7 @@
         <v/>
       </c>
       <c r="N202" s="7"/>
+      <c r="O202" s="9"/>
     </row>
     <row r="203" spans="1:18">
       <c r="G203" s="4"/>
@@ -2520,6 +2862,7 @@
         <v/>
       </c>
       <c r="N203" s="7"/>
+      <c r="O203" s="9"/>
     </row>
     <row r="204" spans="1:18">
       <c r="G204" s="4"/>
@@ -2529,6 +2872,7 @@
         <v/>
       </c>
       <c r="N204" s="7"/>
+      <c r="O204" s="9"/>
     </row>
     <row r="205" spans="1:18">
       <c r="G205" s="4"/>
@@ -2538,6 +2882,7 @@
         <v/>
       </c>
       <c r="N205" s="7"/>
+      <c r="O205" s="9"/>
     </row>
     <row r="206" spans="1:18">
       <c r="G206" s="4"/>
@@ -2547,6 +2892,7 @@
         <v/>
       </c>
       <c r="N206" s="7"/>
+      <c r="O206" s="9"/>
     </row>
     <row r="207" spans="1:18">
       <c r="G207" s="4"/>
@@ -2556,6 +2902,7 @@
         <v/>
       </c>
       <c r="N207" s="7"/>
+      <c r="O207" s="9"/>
     </row>
     <row r="208" spans="1:18">
       <c r="G208" s="4"/>
@@ -2565,6 +2912,7 @@
         <v/>
       </c>
       <c r="N208" s="7"/>
+      <c r="O208" s="9"/>
     </row>
     <row r="209" spans="1:18">
       <c r="G209" s="4"/>
@@ -2574,6 +2922,7 @@
         <v/>
       </c>
       <c r="N209" s="7"/>
+      <c r="O209" s="9"/>
     </row>
     <row r="210" spans="1:18">
       <c r="G210" s="4"/>
@@ -2583,6 +2932,7 @@
         <v/>
       </c>
       <c r="N210" s="7"/>
+      <c r="O210" s="9"/>
     </row>
     <row r="211" spans="1:18">
       <c r="G211" s="4"/>
@@ -2592,6 +2942,7 @@
         <v/>
       </c>
       <c r="N211" s="7"/>
+      <c r="O211" s="9"/>
     </row>
     <row r="212" spans="1:18">
       <c r="G212" s="4"/>
@@ -2601,6 +2952,7 @@
         <v/>
       </c>
       <c r="N212" s="7"/>
+      <c r="O212" s="9"/>
     </row>
     <row r="213" spans="1:18">
       <c r="G213" s="4"/>
@@ -2610,6 +2962,7 @@
         <v/>
       </c>
       <c r="N213" s="7"/>
+      <c r="O213" s="9"/>
     </row>
     <row r="214" spans="1:18">
       <c r="G214" s="4"/>
@@ -2619,6 +2972,7 @@
         <v/>
       </c>
       <c r="N214" s="7"/>
+      <c r="O214" s="9"/>
     </row>
     <row r="215" spans="1:18">
       <c r="G215" s="4"/>
@@ -2628,6 +2982,7 @@
         <v/>
       </c>
       <c r="N215" s="7"/>
+      <c r="O215" s="9"/>
     </row>
     <row r="216" spans="1:18">
       <c r="G216" s="4"/>
@@ -2637,6 +2992,7 @@
         <v/>
       </c>
       <c r="N216" s="7"/>
+      <c r="O216" s="9"/>
     </row>
     <row r="217" spans="1:18">
       <c r="G217" s="4"/>
@@ -2646,6 +3002,7 @@
         <v/>
       </c>
       <c r="N217" s="7"/>
+      <c r="O217" s="9"/>
     </row>
     <row r="218" spans="1:18">
       <c r="G218" s="4"/>
@@ -2655,6 +3012,7 @@
         <v/>
       </c>
       <c r="N218" s="7"/>
+      <c r="O218" s="9"/>
     </row>
     <row r="219" spans="1:18">
       <c r="G219" s="4"/>
@@ -2664,6 +3022,7 @@
         <v/>
       </c>
       <c r="N219" s="7"/>
+      <c r="O219" s="9"/>
     </row>
     <row r="220" spans="1:18">
       <c r="G220" s="4"/>
@@ -2673,6 +3032,7 @@
         <v/>
       </c>
       <c r="N220" s="7"/>
+      <c r="O220" s="9"/>
     </row>
     <row r="221" spans="1:18">
       <c r="G221" s="4"/>
@@ -2682,6 +3042,7 @@
         <v/>
       </c>
       <c r="N221" s="7"/>
+      <c r="O221" s="9"/>
     </row>
     <row r="222" spans="1:18">
       <c r="G222" s="4"/>
@@ -2691,6 +3052,7 @@
         <v/>
       </c>
       <c r="N222" s="7"/>
+      <c r="O222" s="9"/>
     </row>
     <row r="223" spans="1:18">
       <c r="G223" s="4"/>
@@ -2700,6 +3062,7 @@
         <v/>
       </c>
       <c r="N223" s="7"/>
+      <c r="O223" s="9"/>
     </row>
     <row r="224" spans="1:18">
       <c r="G224" s="4"/>
@@ -2709,6 +3072,7 @@
         <v/>
       </c>
       <c r="N224" s="7"/>
+      <c r="O224" s="9"/>
     </row>
     <row r="225" spans="1:18">
       <c r="G225" s="4"/>
@@ -2718,6 +3082,7 @@
         <v/>
       </c>
       <c r="N225" s="7"/>
+      <c r="O225" s="9"/>
     </row>
     <row r="226" spans="1:18">
       <c r="G226" s="4"/>
@@ -2727,6 +3092,7 @@
         <v/>
       </c>
       <c r="N226" s="7"/>
+      <c r="O226" s="9"/>
     </row>
     <row r="227" spans="1:18">
       <c r="G227" s="4"/>
@@ -2736,6 +3102,7 @@
         <v/>
       </c>
       <c r="N227" s="7"/>
+      <c r="O227" s="9"/>
     </row>
     <row r="228" spans="1:18">
       <c r="G228" s="4"/>
@@ -2745,6 +3112,7 @@
         <v/>
       </c>
       <c r="N228" s="7"/>
+      <c r="O228" s="9"/>
     </row>
     <row r="229" spans="1:18">
       <c r="G229" s="4"/>
@@ -2754,6 +3122,7 @@
         <v/>
       </c>
       <c r="N229" s="7"/>
+      <c r="O229" s="9"/>
     </row>
     <row r="230" spans="1:18">
       <c r="G230" s="4"/>
@@ -2763,6 +3132,7 @@
         <v/>
       </c>
       <c r="N230" s="7"/>
+      <c r="O230" s="9"/>
     </row>
     <row r="231" spans="1:18">
       <c r="G231" s="4"/>
@@ -2772,6 +3142,7 @@
         <v/>
       </c>
       <c r="N231" s="7"/>
+      <c r="O231" s="9"/>
     </row>
     <row r="232" spans="1:18">
       <c r="G232" s="4"/>
@@ -2781,6 +3152,7 @@
         <v/>
       </c>
       <c r="N232" s="7"/>
+      <c r="O232" s="9"/>
     </row>
     <row r="233" spans="1:18">
       <c r="G233" s="4"/>
@@ -2790,6 +3162,7 @@
         <v/>
       </c>
       <c r="N233" s="7"/>
+      <c r="O233" s="9"/>
     </row>
     <row r="234" spans="1:18">
       <c r="G234" s="4"/>
@@ -2799,6 +3172,7 @@
         <v/>
       </c>
       <c r="N234" s="7"/>
+      <c r="O234" s="9"/>
     </row>
     <row r="235" spans="1:18">
       <c r="G235" s="4"/>
@@ -2808,6 +3182,7 @@
         <v/>
       </c>
       <c r="N235" s="7"/>
+      <c r="O235" s="9"/>
     </row>
     <row r="236" spans="1:18">
       <c r="G236" s="4"/>
@@ -2817,6 +3192,7 @@
         <v/>
       </c>
       <c r="N236" s="7"/>
+      <c r="O236" s="9"/>
     </row>
     <row r="237" spans="1:18">
       <c r="G237" s="4"/>
@@ -2826,6 +3202,7 @@
         <v/>
       </c>
       <c r="N237" s="7"/>
+      <c r="O237" s="9"/>
     </row>
     <row r="238" spans="1:18">
       <c r="G238" s="4"/>
@@ -2835,6 +3212,7 @@
         <v/>
       </c>
       <c r="N238" s="7"/>
+      <c r="O238" s="9"/>
     </row>
     <row r="239" spans="1:18">
       <c r="G239" s="4"/>
@@ -2844,6 +3222,7 @@
         <v/>
       </c>
       <c r="N239" s="7"/>
+      <c r="O239" s="9"/>
     </row>
     <row r="240" spans="1:18">
       <c r="G240" s="4"/>
@@ -2853,6 +3232,7 @@
         <v/>
       </c>
       <c r="N240" s="7"/>
+      <c r="O240" s="9"/>
     </row>
     <row r="241" spans="1:18">
       <c r="G241" s="4"/>
@@ -2862,6 +3242,7 @@
         <v/>
       </c>
       <c r="N241" s="7"/>
+      <c r="O241" s="9"/>
     </row>
     <row r="242" spans="1:18">
       <c r="G242" s="4"/>
@@ -2871,6 +3252,7 @@
         <v/>
       </c>
       <c r="N242" s="7"/>
+      <c r="O242" s="9"/>
     </row>
     <row r="243" spans="1:18">
       <c r="G243" s="4"/>
@@ -2880,6 +3262,7 @@
         <v/>
       </c>
       <c r="N243" s="7"/>
+      <c r="O243" s="9"/>
     </row>
     <row r="244" spans="1:18">
       <c r="G244" s="4"/>
@@ -2889,6 +3272,7 @@
         <v/>
       </c>
       <c r="N244" s="7"/>
+      <c r="O244" s="9"/>
     </row>
     <row r="245" spans="1:18">
       <c r="G245" s="4"/>
@@ -2898,6 +3282,7 @@
         <v/>
       </c>
       <c r="N245" s="7"/>
+      <c r="O245" s="9"/>
     </row>
     <row r="246" spans="1:18">
       <c r="G246" s="4"/>
@@ -2907,6 +3292,7 @@
         <v/>
       </c>
       <c r="N246" s="7"/>
+      <c r="O246" s="9"/>
     </row>
     <row r="247" spans="1:18">
       <c r="G247" s="4"/>
@@ -2916,6 +3302,7 @@
         <v/>
       </c>
       <c r="N247" s="7"/>
+      <c r="O247" s="9"/>
     </row>
     <row r="248" spans="1:18">
       <c r="G248" s="4"/>
@@ -2925,6 +3312,7 @@
         <v/>
       </c>
       <c r="N248" s="7"/>
+      <c r="O248" s="9"/>
     </row>
     <row r="249" spans="1:18">
       <c r="G249" s="4"/>
@@ -2934,6 +3322,7 @@
         <v/>
       </c>
       <c r="N249" s="7"/>
+      <c r="O249" s="9"/>
     </row>
     <row r="250" spans="1:18">
       <c r="G250" s="4"/>
@@ -2943,6 +3332,7 @@
         <v/>
       </c>
       <c r="N250" s="7"/>
+      <c r="O250" s="9"/>
     </row>
     <row r="251" spans="1:18">
       <c r="G251" s="4"/>
@@ -2952,6 +3342,7 @@
         <v/>
       </c>
       <c r="N251" s="7"/>
+      <c r="O251" s="9"/>
     </row>
     <row r="252" spans="1:18">
       <c r="G252" s="4"/>
@@ -2961,6 +3352,7 @@
         <v/>
       </c>
       <c r="N252" s="7"/>
+      <c r="O252" s="9"/>
     </row>
     <row r="253" spans="1:18">
       <c r="G253" s="4"/>
@@ -2970,6 +3362,7 @@
         <v/>
       </c>
       <c r="N253" s="7"/>
+      <c r="O253" s="9"/>
     </row>
     <row r="254" spans="1:18">
       <c r="G254" s="4"/>
@@ -2979,6 +3372,7 @@
         <v/>
       </c>
       <c r="N254" s="7"/>
+      <c r="O254" s="9"/>
     </row>
     <row r="255" spans="1:18">
       <c r="G255" s="4"/>
@@ -2988,6 +3382,7 @@
         <v/>
       </c>
       <c r="N255" s="7"/>
+      <c r="O255" s="9"/>
     </row>
     <row r="256" spans="1:18">
       <c r="G256" s="4"/>
@@ -2997,6 +3392,7 @@
         <v/>
       </c>
       <c r="N256" s="7"/>
+      <c r="O256" s="9"/>
     </row>
     <row r="257" spans="1:18">
       <c r="G257" s="4"/>
@@ -3006,6 +3402,7 @@
         <v/>
       </c>
       <c r="N257" s="7"/>
+      <c r="O257" s="9"/>
     </row>
     <row r="258" spans="1:18">
       <c r="G258" s="4"/>
@@ -3015,6 +3412,7 @@
         <v/>
       </c>
       <c r="N258" s="7"/>
+      <c r="O258" s="9"/>
     </row>
     <row r="259" spans="1:18">
       <c r="G259" s="4"/>
@@ -3024,6 +3422,7 @@
         <v/>
       </c>
       <c r="N259" s="7"/>
+      <c r="O259" s="9"/>
     </row>
     <row r="260" spans="1:18">
       <c r="G260" s="4"/>
@@ -3033,6 +3432,7 @@
         <v/>
       </c>
       <c r="N260" s="7"/>
+      <c r="O260" s="9"/>
     </row>
     <row r="261" spans="1:18">
       <c r="G261" s="4"/>
@@ -3042,6 +3442,7 @@
         <v/>
       </c>
       <c r="N261" s="7"/>
+      <c r="O261" s="9"/>
     </row>
     <row r="262" spans="1:18">
       <c r="G262" s="4"/>
@@ -3051,6 +3452,7 @@
         <v/>
       </c>
       <c r="N262" s="7"/>
+      <c r="O262" s="9"/>
     </row>
     <row r="263" spans="1:18">
       <c r="G263" s="4"/>
@@ -3060,6 +3462,7 @@
         <v/>
       </c>
       <c r="N263" s="7"/>
+      <c r="O263" s="9"/>
     </row>
     <row r="264" spans="1:18">
       <c r="G264" s="4"/>
@@ -3069,6 +3472,7 @@
         <v/>
       </c>
       <c r="N264" s="7"/>
+      <c r="O264" s="9"/>
     </row>
     <row r="265" spans="1:18">
       <c r="G265" s="4"/>
@@ -3078,6 +3482,7 @@
         <v/>
       </c>
       <c r="N265" s="7"/>
+      <c r="O265" s="9"/>
     </row>
     <row r="266" spans="1:18">
       <c r="G266" s="4"/>
@@ -3087,6 +3492,7 @@
         <v/>
       </c>
       <c r="N266" s="7"/>
+      <c r="O266" s="9"/>
     </row>
     <row r="267" spans="1:18">
       <c r="G267" s="4"/>
@@ -3096,6 +3502,7 @@
         <v/>
       </c>
       <c r="N267" s="7"/>
+      <c r="O267" s="9"/>
     </row>
     <row r="268" spans="1:18">
       <c r="G268" s="4"/>
@@ -3105,6 +3512,7 @@
         <v/>
       </c>
       <c r="N268" s="7"/>
+      <c r="O268" s="9"/>
     </row>
     <row r="269" spans="1:18">
       <c r="G269" s="4"/>
@@ -3114,6 +3522,7 @@
         <v/>
       </c>
       <c r="N269" s="7"/>
+      <c r="O269" s="9"/>
     </row>
     <row r="270" spans="1:18">
       <c r="G270" s="4"/>
@@ -3123,6 +3532,7 @@
         <v/>
       </c>
       <c r="N270" s="7"/>
+      <c r="O270" s="9"/>
     </row>
     <row r="271" spans="1:18">
       <c r="G271" s="4"/>
@@ -3132,6 +3542,7 @@
         <v/>
       </c>
       <c r="N271" s="7"/>
+      <c r="O271" s="9"/>
     </row>
     <row r="272" spans="1:18">
       <c r="G272" s="4"/>
@@ -3141,6 +3552,7 @@
         <v/>
       </c>
       <c r="N272" s="7"/>
+      <c r="O272" s="9"/>
     </row>
     <row r="273" spans="1:18">
       <c r="G273" s="4"/>
@@ -3150,6 +3562,7 @@
         <v/>
       </c>
       <c r="N273" s="7"/>
+      <c r="O273" s="9"/>
     </row>
     <row r="274" spans="1:18">
       <c r="G274" s="4"/>
@@ -3159,6 +3572,7 @@
         <v/>
       </c>
       <c r="N274" s="7"/>
+      <c r="O274" s="9"/>
     </row>
     <row r="275" spans="1:18">
       <c r="G275" s="4"/>
@@ -3168,6 +3582,7 @@
         <v/>
       </c>
       <c r="N275" s="7"/>
+      <c r="O275" s="9"/>
     </row>
     <row r="276" spans="1:18">
       <c r="G276" s="4"/>
@@ -3177,6 +3592,7 @@
         <v/>
       </c>
       <c r="N276" s="7"/>
+      <c r="O276" s="9"/>
     </row>
     <row r="277" spans="1:18">
       <c r="G277" s="4"/>
@@ -3186,6 +3602,7 @@
         <v/>
       </c>
       <c r="N277" s="7"/>
+      <c r="O277" s="9"/>
     </row>
     <row r="278" spans="1:18">
       <c r="G278" s="4"/>
@@ -3195,6 +3612,7 @@
         <v/>
       </c>
       <c r="N278" s="7"/>
+      <c r="O278" s="9"/>
     </row>
     <row r="279" spans="1:18">
       <c r="G279" s="4"/>
@@ -3204,6 +3622,7 @@
         <v/>
       </c>
       <c r="N279" s="7"/>
+      <c r="O279" s="9"/>
     </row>
     <row r="280" spans="1:18">
       <c r="G280" s="4"/>
@@ -3213,6 +3632,7 @@
         <v/>
       </c>
       <c r="N280" s="7"/>
+      <c r="O280" s="9"/>
     </row>
     <row r="281" spans="1:18">
       <c r="G281" s="4"/>
@@ -3222,6 +3642,7 @@
         <v/>
       </c>
       <c r="N281" s="7"/>
+      <c r="O281" s="9"/>
     </row>
     <row r="282" spans="1:18">
       <c r="G282" s="4"/>
@@ -3231,6 +3652,7 @@
         <v/>
       </c>
       <c r="N282" s="7"/>
+      <c r="O282" s="9"/>
     </row>
     <row r="283" spans="1:18">
       <c r="G283" s="4"/>
@@ -3240,6 +3662,7 @@
         <v/>
       </c>
       <c r="N283" s="7"/>
+      <c r="O283" s="9"/>
     </row>
     <row r="284" spans="1:18">
       <c r="G284" s="4"/>
@@ -3249,6 +3672,7 @@
         <v/>
       </c>
       <c r="N284" s="7"/>
+      <c r="O284" s="9"/>
     </row>
     <row r="285" spans="1:18">
       <c r="G285" s="4"/>
@@ -3258,6 +3682,7 @@
         <v/>
       </c>
       <c r="N285" s="7"/>
+      <c r="O285" s="9"/>
     </row>
     <row r="286" spans="1:18">
       <c r="G286" s="4"/>
@@ -3267,6 +3692,7 @@
         <v/>
       </c>
       <c r="N286" s="7"/>
+      <c r="O286" s="9"/>
     </row>
     <row r="287" spans="1:18">
       <c r="G287" s="4"/>
@@ -3276,6 +3702,7 @@
         <v/>
       </c>
       <c r="N287" s="7"/>
+      <c r="O287" s="9"/>
     </row>
     <row r="288" spans="1:18">
       <c r="G288" s="4"/>
@@ -3285,6 +3712,7 @@
         <v/>
       </c>
       <c r="N288" s="7"/>
+      <c r="O288" s="9"/>
     </row>
     <row r="289" spans="1:18">
       <c r="G289" s="4"/>
@@ -3294,6 +3722,7 @@
         <v/>
       </c>
       <c r="N289" s="7"/>
+      <c r="O289" s="9"/>
     </row>
     <row r="290" spans="1:18">
       <c r="G290" s="4"/>
@@ -3303,6 +3732,7 @@
         <v/>
       </c>
       <c r="N290" s="7"/>
+      <c r="O290" s="9"/>
     </row>
     <row r="291" spans="1:18">
       <c r="G291" s="4"/>
@@ -3312,6 +3742,7 @@
         <v/>
       </c>
       <c r="N291" s="7"/>
+      <c r="O291" s="9"/>
     </row>
     <row r="292" spans="1:18">
       <c r="G292" s="4"/>
@@ -3321,6 +3752,7 @@
         <v/>
       </c>
       <c r="N292" s="7"/>
+      <c r="O292" s="9"/>
     </row>
     <row r="293" spans="1:18">
       <c r="G293" s="4"/>
@@ -3330,6 +3762,7 @@
         <v/>
       </c>
       <c r="N293" s="7"/>
+      <c r="O293" s="9"/>
     </row>
     <row r="294" spans="1:18">
       <c r="G294" s="4"/>
@@ -3339,6 +3772,7 @@
         <v/>
       </c>
       <c r="N294" s="7"/>
+      <c r="O294" s="9"/>
     </row>
     <row r="295" spans="1:18">
       <c r="G295" s="4"/>
@@ -3348,6 +3782,7 @@
         <v/>
       </c>
       <c r="N295" s="7"/>
+      <c r="O295" s="9"/>
     </row>
     <row r="296" spans="1:18">
       <c r="G296" s="4"/>
@@ -3357,6 +3792,7 @@
         <v/>
       </c>
       <c r="N296" s="7"/>
+      <c r="O296" s="9"/>
     </row>
     <row r="297" spans="1:18">
       <c r="G297" s="4"/>
@@ -3366,6 +3802,7 @@
         <v/>
       </c>
       <c r="N297" s="7"/>
+      <c r="O297" s="9"/>
     </row>
     <row r="298" spans="1:18">
       <c r="G298" s="4"/>
@@ -3375,6 +3812,7 @@
         <v/>
       </c>
       <c r="N298" s="7"/>
+      <c r="O298" s="9"/>
     </row>
     <row r="299" spans="1:18">
       <c r="G299" s="4"/>
@@ -3384,6 +3822,7 @@
         <v/>
       </c>
       <c r="N299" s="7"/>
+      <c r="O299" s="9"/>
     </row>
     <row r="300" spans="1:18">
       <c r="G300" s="4"/>
@@ -3393,6 +3832,7 @@
         <v/>
       </c>
       <c r="N300" s="7"/>
+      <c r="O300" s="9"/>
     </row>
     <row r="301" spans="1:18">
       <c r="G301" s="4"/>
@@ -3402,6 +3842,7 @@
         <v/>
       </c>
       <c r="N301" s="7"/>
+      <c r="O301" s="9"/>
     </row>
     <row r="302" spans="1:18">
       <c r="G302" s="4"/>
@@ -3411,6 +3852,7 @@
         <v/>
       </c>
       <c r="N302" s="7"/>
+      <c r="O302" s="9"/>
     </row>
     <row r="303" spans="1:18">
       <c r="G303" s="4"/>
@@ -3420,6 +3862,7 @@
         <v/>
       </c>
       <c r="N303" s="7"/>
+      <c r="O303" s="9"/>
     </row>
     <row r="304" spans="1:18">
       <c r="G304" s="4"/>
@@ -3429,6 +3872,7 @@
         <v/>
       </c>
       <c r="N304" s="7"/>
+      <c r="O304" s="9"/>
     </row>
     <row r="305" spans="1:18">
       <c r="G305" s="4"/>
@@ -3438,6 +3882,7 @@
         <v/>
       </c>
       <c r="N305" s="7"/>
+      <c r="O305" s="9"/>
     </row>
     <row r="306" spans="1:18">
       <c r="G306" s="4"/>
@@ -3447,6 +3892,7 @@
         <v/>
       </c>
       <c r="N306" s="7"/>
+      <c r="O306" s="9"/>
     </row>
     <row r="307" spans="1:18">
       <c r="G307" s="4"/>
@@ -3456,6 +3902,7 @@
         <v/>
       </c>
       <c r="N307" s="7"/>
+      <c r="O307" s="9"/>
     </row>
     <row r="308" spans="1:18">
       <c r="G308" s="4"/>
@@ -3465,6 +3912,7 @@
         <v/>
       </c>
       <c r="N308" s="7"/>
+      <c r="O308" s="9"/>
     </row>
     <row r="309" spans="1:18">
       <c r="G309" s="4"/>
@@ -3474,6 +3922,7 @@
         <v/>
       </c>
       <c r="N309" s="7"/>
+      <c r="O309" s="9"/>
     </row>
     <row r="310" spans="1:18">
       <c r="G310" s="4"/>
@@ -3483,6 +3932,7 @@
         <v/>
       </c>
       <c r="N310" s="7"/>
+      <c r="O310" s="9"/>
     </row>
     <row r="311" spans="1:18">
       <c r="G311" s="4"/>
@@ -3492,6 +3942,7 @@
         <v/>
       </c>
       <c r="N311" s="7"/>
+      <c r="O311" s="9"/>
     </row>
     <row r="312" spans="1:18">
       <c r="G312" s="4"/>
@@ -3501,6 +3952,7 @@
         <v/>
       </c>
       <c r="N312" s="7"/>
+      <c r="O312" s="9"/>
     </row>
     <row r="313" spans="1:18">
       <c r="G313" s="4"/>
@@ -3510,6 +3962,7 @@
         <v/>
       </c>
       <c r="N313" s="7"/>
+      <c r="O313" s="9"/>
     </row>
     <row r="314" spans="1:18">
       <c r="G314" s="4"/>
@@ -3519,6 +3972,7 @@
         <v/>
       </c>
       <c r="N314" s="7"/>
+      <c r="O314" s="9"/>
     </row>
     <row r="315" spans="1:18">
       <c r="G315" s="4"/>
@@ -3528,6 +3982,7 @@
         <v/>
       </c>
       <c r="N315" s="7"/>
+      <c r="O315" s="9"/>
     </row>
     <row r="316" spans="1:18">
       <c r="G316" s="4"/>
@@ -3537,6 +3992,7 @@
         <v/>
       </c>
       <c r="N316" s="7"/>
+      <c r="O316" s="9"/>
     </row>
     <row r="317" spans="1:18">
       <c r="G317" s="4"/>
@@ -3546,6 +4002,7 @@
         <v/>
       </c>
       <c r="N317" s="7"/>
+      <c r="O317" s="9"/>
     </row>
     <row r="318" spans="1:18">
       <c r="G318" s="4"/>
@@ -3555,6 +4012,7 @@
         <v/>
       </c>
       <c r="N318" s="7"/>
+      <c r="O318" s="9"/>
     </row>
     <row r="319" spans="1:18">
       <c r="G319" s="4"/>
@@ -3564,6 +4022,7 @@
         <v/>
       </c>
       <c r="N319" s="7"/>
+      <c r="O319" s="9"/>
     </row>
     <row r="320" spans="1:18">
       <c r="G320" s="4"/>
@@ -3573,6 +4032,7 @@
         <v/>
       </c>
       <c r="N320" s="7"/>
+      <c r="O320" s="9"/>
     </row>
     <row r="321" spans="1:18">
       <c r="G321" s="4"/>
@@ -3582,6 +4042,7 @@
         <v/>
       </c>
       <c r="N321" s="7"/>
+      <c r="O321" s="9"/>
     </row>
     <row r="322" spans="1:18">
       <c r="G322" s="4"/>
@@ -3591,6 +4052,7 @@
         <v/>
       </c>
       <c r="N322" s="7"/>
+      <c r="O322" s="9"/>
     </row>
     <row r="323" spans="1:18">
       <c r="G323" s="4"/>
@@ -3600,6 +4062,7 @@
         <v/>
       </c>
       <c r="N323" s="7"/>
+      <c r="O323" s="9"/>
     </row>
     <row r="324" spans="1:18">
       <c r="G324" s="4"/>
@@ -3609,6 +4072,7 @@
         <v/>
       </c>
       <c r="N324" s="7"/>
+      <c r="O324" s="9"/>
     </row>
     <row r="325" spans="1:18">
       <c r="G325" s="4"/>
@@ -3618,6 +4082,7 @@
         <v/>
       </c>
       <c r="N325" s="7"/>
+      <c r="O325" s="9"/>
     </row>
     <row r="326" spans="1:18">
       <c r="G326" s="4"/>
@@ -3627,6 +4092,7 @@
         <v/>
       </c>
       <c r="N326" s="7"/>
+      <c r="O326" s="9"/>
     </row>
     <row r="327" spans="1:18">
       <c r="G327" s="4"/>
@@ -3636,6 +4102,7 @@
         <v/>
       </c>
       <c r="N327" s="7"/>
+      <c r="O327" s="9"/>
     </row>
     <row r="328" spans="1:18">
       <c r="G328" s="4"/>
@@ -3645,6 +4112,7 @@
         <v/>
       </c>
       <c r="N328" s="7"/>
+      <c r="O328" s="9"/>
     </row>
     <row r="329" spans="1:18">
       <c r="G329" s="4"/>
@@ -3654,6 +4122,7 @@
         <v/>
       </c>
       <c r="N329" s="7"/>
+      <c r="O329" s="9"/>
     </row>
     <row r="330" spans="1:18">
       <c r="G330" s="4"/>
@@ -3663,6 +4132,7 @@
         <v/>
       </c>
       <c r="N330" s="7"/>
+      <c r="O330" s="9"/>
     </row>
     <row r="331" spans="1:18">
       <c r="G331" s="4"/>
@@ -3672,6 +4142,7 @@
         <v/>
       </c>
       <c r="N331" s="7"/>
+      <c r="O331" s="9"/>
     </row>
     <row r="332" spans="1:18">
       <c r="G332" s="4"/>
@@ -3681,6 +4152,7 @@
         <v/>
       </c>
       <c r="N332" s="7"/>
+      <c r="O332" s="9"/>
     </row>
     <row r="333" spans="1:18">
       <c r="G333" s="4"/>
@@ -3690,6 +4162,7 @@
         <v/>
       </c>
       <c r="N333" s="7"/>
+      <c r="O333" s="9"/>
     </row>
     <row r="334" spans="1:18">
       <c r="G334" s="4"/>
@@ -3699,6 +4172,7 @@
         <v/>
       </c>
       <c r="N334" s="7"/>
+      <c r="O334" s="9"/>
     </row>
     <row r="335" spans="1:18">
       <c r="G335" s="4"/>
@@ -3708,6 +4182,7 @@
         <v/>
       </c>
       <c r="N335" s="7"/>
+      <c r="O335" s="9"/>
     </row>
     <row r="336" spans="1:18">
       <c r="G336" s="4"/>
@@ -3717,6 +4192,7 @@
         <v/>
       </c>
       <c r="N336" s="7"/>
+      <c r="O336" s="9"/>
     </row>
     <row r="337" spans="1:18">
       <c r="G337" s="4"/>
@@ -3726,6 +4202,7 @@
         <v/>
       </c>
       <c r="N337" s="7"/>
+      <c r="O337" s="9"/>
     </row>
     <row r="338" spans="1:18">
       <c r="G338" s="4"/>
@@ -3735,6 +4212,7 @@
         <v/>
       </c>
       <c r="N338" s="7"/>
+      <c r="O338" s="9"/>
     </row>
     <row r="339" spans="1:18">
       <c r="G339" s="4"/>
@@ -3744,6 +4222,7 @@
         <v/>
       </c>
       <c r="N339" s="7"/>
+      <c r="O339" s="9"/>
     </row>
     <row r="340" spans="1:18">
       <c r="G340" s="4"/>
@@ -3753,6 +4232,7 @@
         <v/>
       </c>
       <c r="N340" s="7"/>
+      <c r="O340" s="9"/>
     </row>
     <row r="341" spans="1:18">
       <c r="G341" s="4"/>
@@ -3762,6 +4242,7 @@
         <v/>
       </c>
       <c r="N341" s="7"/>
+      <c r="O341" s="9"/>
     </row>
     <row r="342" spans="1:18">
       <c r="G342" s="4"/>
@@ -3771,6 +4252,7 @@
         <v/>
       </c>
       <c r="N342" s="7"/>
+      <c r="O342" s="9"/>
     </row>
     <row r="343" spans="1:18">
       <c r="G343" s="4"/>
@@ -3780,6 +4262,7 @@
         <v/>
       </c>
       <c r="N343" s="7"/>
+      <c r="O343" s="9"/>
     </row>
     <row r="344" spans="1:18">
       <c r="G344" s="4"/>
@@ -3789,6 +4272,7 @@
         <v/>
       </c>
       <c r="N344" s="7"/>
+      <c r="O344" s="9"/>
     </row>
     <row r="345" spans="1:18">
       <c r="G345" s="4"/>
@@ -3798,6 +4282,7 @@
         <v/>
       </c>
       <c r="N345" s="7"/>
+      <c r="O345" s="9"/>
     </row>
     <row r="346" spans="1:18">
       <c r="G346" s="4"/>
@@ -3807,6 +4292,7 @@
         <v/>
       </c>
       <c r="N346" s="7"/>
+      <c r="O346" s="9"/>
     </row>
     <row r="347" spans="1:18">
       <c r="G347" s="4"/>
@@ -3816,6 +4302,7 @@
         <v/>
       </c>
       <c r="N347" s="7"/>
+      <c r="O347" s="9"/>
     </row>
     <row r="348" spans="1:18">
       <c r="G348" s="4"/>
@@ -3825,6 +4312,7 @@
         <v/>
       </c>
       <c r="N348" s="7"/>
+      <c r="O348" s="9"/>
     </row>
     <row r="349" spans="1:18">
       <c r="G349" s="4"/>
@@ -3834,6 +4322,7 @@
         <v/>
       </c>
       <c r="N349" s="7"/>
+      <c r="O349" s="9"/>
     </row>
     <row r="350" spans="1:18">
       <c r="G350" s="4"/>
@@ -3843,6 +4332,7 @@
         <v/>
       </c>
       <c r="N350" s="7"/>
+      <c r="O350" s="10"/>
     </row>
     <row r="351" spans="1:18">
       <c r="G351" s="4"/>
@@ -3852,6 +4342,7 @@
         <v/>
       </c>
       <c r="N351" s="7"/>
+      <c r="O351" s="10"/>
     </row>
     <row r="352" spans="1:18">
       <c r="G352" s="4"/>
@@ -3861,6 +4352,7 @@
         <v/>
       </c>
       <c r="N352" s="7"/>
+      <c r="O352" s="10"/>
     </row>
     <row r="353" spans="1:18">
       <c r="G353" s="4"/>
@@ -3870,6 +4362,7 @@
         <v/>
       </c>
       <c r="N353" s="7"/>
+      <c r="O353" s="10"/>
     </row>
     <row r="354" spans="1:18">
       <c r="G354" s="4"/>
@@ -3879,6 +4372,7 @@
         <v/>
       </c>
       <c r="N354" s="7"/>
+      <c r="O354" s="10"/>
     </row>
     <row r="355" spans="1:18">
       <c r="G355" s="4"/>
@@ -3888,6 +4382,7 @@
         <v/>
       </c>
       <c r="N355" s="7"/>
+      <c r="O355" s="10"/>
     </row>
     <row r="356" spans="1:18">
       <c r="G356" s="4"/>
@@ -3897,6 +4392,7 @@
         <v/>
       </c>
       <c r="N356" s="7"/>
+      <c r="O356" s="10"/>
     </row>
     <row r="357" spans="1:18">
       <c r="G357" s="4"/>
@@ -10379,7 +10875,7 @@
   <mergeCells>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A1:G5"/>
-    <mergeCell ref="I1:N6"/>
+    <mergeCell ref="I1:O6"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
